--- a/output/reports/cv_experiment_KNN_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_qcut_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.160219430923462</v>
+        <v>4.643058776855469</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9068486871628831</v>
+        <v>0.8817259419285336</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9059263521288837</v>
+        <v>0.893083354446415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.905775679947079</v>
+        <v>0.892181422544394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9730886664785278</v>
+        <v>0.9553259504952031</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.176057577133179</v>
+        <v>5.089538812637329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9074944225235356</v>
+        <v>0.8868223809415141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9059263521288837</v>
+        <v>0.8915632125665062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.905775679947079</v>
+        <v>0.8905966180796685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9730886664785278</v>
+        <v>0.9587230118259739</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.359708309173584</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9084982920403439</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9059263521288837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.905775679947079</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9730886664785278</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.699659585952759</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.909212576060211</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9059263521288837</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.905775679947079</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9730886664785278</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.160219430923462</v>
+        <v>4.643058776855469</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9068486871628831</v>
+        <v>0.8817259419285336</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9059263521288837</v>
+        <v>0.893083354446415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.905775679947079</v>
+        <v>0.892181422544394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9730886664785278</v>
+        <v>0.9553259504952031</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.176057577133179</v>
+        <v>5.089538812637329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9074944225235356</v>
+        <v>0.8868223809415141</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9059263521288837</v>
+        <v>0.8915632125665062</v>
       </c>
       <c r="G3" t="n">
-        <v>0.905775679947079</v>
+        <v>0.8905966180796685</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9730886664785278</v>
+        <v>0.9587230118259739</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.359708309173584</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9084982920403439</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9059263521288837</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.905775679947079</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9730886664785278</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.699659585952759</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.909212576060211</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9059263521288837</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.905775679947079</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9730886664785278</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.643058776855469</v>
+        <v>0.06891679763793945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8817259419285336</v>
+        <v>0.9869704489949077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.893083354446415</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G2" t="n">
-        <v>0.892181422544394</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9553259504952031</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.089538812637329</v>
+        <v>0.06421852111816406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8868223809415141</v>
+        <v>0.9837078852912551</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8915632125665062</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8905966180796685</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9587230118259739</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.643058776855469</v>
+        <v>0.06891679763793945</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8817259419285336</v>
+        <v>0.9869704489949077</v>
       </c>
       <c r="F2" t="n">
-        <v>0.893083354446415</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G2" t="n">
-        <v>0.892181422544394</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9553259504952031</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.089538812637329</v>
+        <v>0.06421852111816406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8868223809415141</v>
+        <v>0.9837078852912551</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8915632125665062</v>
+        <v>0.974025974025974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8905966180796685</v>
+        <v>0.9738673001866622</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9587230118259739</v>
+        <v>0.9929577464788731</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 9, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_qcut_classification.xlsx
+++ b/output/reports/cv_experiment_KNN_qcut_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06891679763793945</v>
+        <v>0.1603937149047852</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9869704489949077</v>
+        <v>0.6220988350946945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.974025974025974</v>
+        <v>0.7372881355932204</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.7020914749921888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9929577464788731</v>
+        <v>0.8840491238149958</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06421852111816406</v>
+        <v>0.1739106178283691</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9837078852912551</v>
+        <v>0.6580144179369923</v>
       </c>
       <c r="F3" t="n">
-        <v>0.974025974025974</v>
+        <v>0.7372881355932204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.7020914749921888</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9929577464788731</v>
+        <v>0.8840491238149958</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06891679763793945</v>
+        <v>0.1603937149047852</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9869704489949077</v>
+        <v>0.6220988350946945</v>
       </c>
       <c r="F2" t="n">
-        <v>0.974025974025974</v>
+        <v>0.7372881355932204</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.7020914749921888</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9929577464788731</v>
+        <v>0.8840491238149958</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.06421852111816406</v>
+        <v>0.1739106178283691</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9837078852912551</v>
+        <v>0.6580144179369923</v>
       </c>
       <c r="F3" t="n">
-        <v>0.974025974025974</v>
+        <v>0.7372881355932204</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9738673001866622</v>
+        <v>0.7020914749921888</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9929577464788731</v>
+        <v>0.8840491238149958</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
